--- a/data/trending_integrated_20261020_09.xlsx
+++ b/data/trending_integrated_20261020_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43050</v>
+        <v>1843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+5.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>359</v>
+        <v>121</v>
       </c>
       <c r="H2" t="n">
-        <v>13.11</v>
+        <v>1.77</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42950</v>
+        <v>1748</v>
       </c>
       <c r="K2" t="n">
-        <v>42600</v>
+        <v>1706</v>
       </c>
       <c r="L2" t="n">
-        <v>43100</v>
+        <v>1895</v>
       </c>
       <c r="M2" t="n">
-        <v>42600</v>
+        <v>1661</v>
       </c>
       <c r="N2" t="n">
-        <v>13.04</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>770796850</v>
+        <v>30020485609</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>2970</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>890</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,29 +626,397 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB, 담관암 FDA 승인 관련 기대감과 불확실성 혼재. 김태한 회장 및 진양곤 의장 언급.</t>
+          <t>스페이스X 관련주로 부각되며 3거래일간 33.95% 상승. 직납 기대감 및 2차 랠리 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', 'Class1']</t>
+          <t>['스페이스X', '직납', '철강']</t>
         </is>
       </c>
       <c r="X2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>008970</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>42400</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'-1.28%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G3" t="n">
+        <v>371</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>42950</v>
+      </c>
+      <c r="K3" t="n">
+        <v>42600</v>
+      </c>
+      <c r="L3" t="n">
+        <v>43200</v>
+      </c>
+      <c r="M3" t="n">
+        <v>42300</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2505689775</v>
+      </c>
+      <c r="P3" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>HLB그룹 바이오 부문 총괄회장 발언 및 담관암 FDA 승인 기대감. Class1 발표에 따른 주가 변동성 예상 및 매수 기회 언급.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['HLB', '담관암', 'FDA승인']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>7</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>214500</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-1.61%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>454</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2660</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>218000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>219500</v>
+      </c>
+      <c r="L4" t="n">
+        <v>219500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>213000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="O4" t="n">
+        <v>364569326000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>국내 정치 이슈와 미국 반도체 시장 현황 및 중국 창신메모리 실적 둔화 소식 혼재. 반도체 업황에 대한 엇갈린 전망.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['정치', '반도체', '실적']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1216000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-4.78%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>504</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="H5" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1277000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1265000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1267000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1215000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="O5" t="n">
+        <v>541956859000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>465500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>솔리다임 관련 이슈 및 최태원 회장 관련 부정적 언급. 주주 가치 훼손 및 중복 상장 논란으로 인한 주가 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['솔리다임', '최태원', '중복상장']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>73700</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-10.12%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L6" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M6" t="n">
+        <v>73400</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O6" t="n">
+        <v>18675939700</v>
+      </c>
+      <c r="P6" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>공매도 비중 증가 및 주가 급락세 지속. 5만원대 적정가 주장과 함께 향후 주가 하락 전망 및 기관 매수세 기대.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['공매도', '주가하락', '기관']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>272210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_09.xlsx
+++ b/data/trending_integrated_20261020_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1843</v>
+        <v>10740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+5.43%</t>
+          <t>'+17.76%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77</v>
+        <v>0.88</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1748</v>
+        <v>9120</v>
       </c>
       <c r="K2" t="n">
-        <v>1706</v>
+        <v>9500</v>
       </c>
       <c r="L2" t="n">
-        <v>1895</v>
+        <v>11180</v>
       </c>
       <c r="M2" t="n">
-        <v>1661</v>
+        <v>9470</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>30020485609</v>
+        <v>96156803780</v>
       </c>
       <c r="P2" t="n">
-        <v>2970</v>
+        <v>11180</v>
       </c>
       <c r="Q2" t="n">
-        <v>890</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 부각되며 3거래일간 33.95% 상승. 직납 기대감 및 2차 랠리 가능성 언급.</t>
+          <t>로봇, ESS, 이차전지 사업 연관성 및 높은 기대감. 신고가 돌파 및 목표가 상향 조정.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '직납', '철강']</t>
+          <t>['로봇', '신고가', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42400</v>
+        <v>1824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>371</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
-        <v>13.11</v>
+        <v>1.77</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>42950</v>
+        <v>1748</v>
       </c>
       <c r="K3" t="n">
-        <v>42600</v>
+        <v>1706</v>
       </c>
       <c r="L3" t="n">
-        <v>43200</v>
+        <v>1895</v>
       </c>
       <c r="M3" t="n">
-        <v>42300</v>
+        <v>1661</v>
       </c>
       <c r="N3" t="n">
-        <v>13.04</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>2505689775</v>
+        <v>43102357102</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>2970</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>890</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB그룹 바이오 부문 총괄회장 발언 및 담관암 FDA 승인 기대감. Class1 발표에 따른 주가 변동성 예상 및 매수 기회 언급.</t>
+          <t>스페이스X 직납 이슈로 인한 주가 급등 기대감. 최근 3일간 코스피 수익률 3위 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['HLB', '담관암', 'FDA승인']</t>
+          <t>['스페이스X', '철강', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>214500</v>
+        <v>215250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="G4" t="n">
-        <v>2660</v>
+        <v>2245</v>
       </c>
       <c r="H4" t="n">
         <v>46.04</v>
@@ -794,7 +794,7 @@
         <v>45.99</v>
       </c>
       <c r="O4" t="n">
-        <v>364569326000</v>
+        <v>484740285250</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국내 정치 이슈와 미국 반도체 시장 현황 및 중국 창신메모리 실적 둔화 소식 혼재. 반도체 업황에 대한 엇갈린 전망.</t>
+          <t>정치 관련 언급이 다수이며, 반도체 섹터 전반의 혼조세 속 삼성전자 주가 하락.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '실적']</t>
+          <t>['반도체', '정치', '하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,60 +839,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1216000</v>
+        <v>42000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>504</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>1481</v>
+        <v>414</v>
       </c>
       <c r="H5" t="n">
-        <v>48.81</v>
+        <v>13.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1277000</v>
+        <v>42950</v>
       </c>
       <c r="K5" t="n">
-        <v>1265000</v>
+        <v>42600</v>
       </c>
       <c r="L5" t="n">
-        <v>1267000</v>
+        <v>43200</v>
       </c>
       <c r="M5" t="n">
-        <v>1215000</v>
+        <v>41950</v>
       </c>
       <c r="N5" t="n">
-        <v>48.82</v>
+        <v>13.04</v>
       </c>
       <c r="O5" t="n">
-        <v>541956859000</v>
+        <v>3941269325</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>465500</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 관련 이슈 및 최태원 회장 관련 부정적 언급. 주주 가치 훼손 및 중복 상장 논란으로 인한 주가 하락 우려.</t>
+          <t>C1 관련 FDA 승인 결과에 대한 기대와 우려 공존. 주가 방향성 불확실성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '중복상장']</t>
+          <t>['C1', 'FDA 승인', '불확실성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73700</v>
+        <v>1226000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-10.12%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>535</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>1415</v>
       </c>
       <c r="H6" t="n">
-        <v>9.380000000000001</v>
+        <v>48.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>82000</v>
+        <v>1277000</v>
       </c>
       <c r="K6" t="n">
-        <v>79400</v>
+        <v>1265000</v>
       </c>
       <c r="L6" t="n">
-        <v>79400</v>
+        <v>1267000</v>
       </c>
       <c r="M6" t="n">
-        <v>73400</v>
+        <v>1213000</v>
       </c>
       <c r="N6" t="n">
-        <v>9.44</v>
+        <v>48.82</v>
       </c>
       <c r="O6" t="n">
-        <v>18675939700</v>
+        <v>764801157500</v>
       </c>
       <c r="P6" t="n">
-        <v>184000</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>44750</v>
+        <v>465500</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,27 +994,119 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 비중 증가 및 주가 급락세 지속. 5만원대 적정가 주장과 함께 향후 주가 하락 전망 및 기관 매수세 기대.</t>
+          <t>솔리다임 상장 철회 요구 및 경영진에 대한 강한 불만 표출. 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['솔리다임', '경영진', '하락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>74400</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-9.27%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E7" t="n">
+        <v>57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>140</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L7" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>73200</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O7" t="n">
+        <v>28816139450</v>
+      </c>
+      <c r="P7" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>공매도 비중 증가 및 주가 급락에 대한 불만. 투자자들의 부정적 심리 관찰.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>0.3</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>['공매도', '주가하락', '기관']</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['공매도', '급락', '변동성']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>272210</t>
         </is>

--- a/data/trending_integrated_20261020_09.xlsx
+++ b/data/trending_integrated_20261020_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10740</v>
+        <v>11150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.76%</t>
+          <t>'+22.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -610,7 +610,7 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>96156803780</v>
+        <v>111968802860</v>
       </c>
       <c r="P2" t="n">
         <v>11180</v>
@@ -619,14 +619,14 @@
         <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>382000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 사업 연관성 및 높은 기대감. 신고가 돌파 및 목표가 상향 조정.</t>
+          <t>로봇, ESS, 이차전지 테마 복합으로 4일간 45.22% 급등. 7천억 수주잔고 기반 1조 시총 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '신고가', '목표가']</t>
+          <t>['로봇', '수주잔고', '메가트렌드']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1824</v>
+        <v>20750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+5.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>3.07</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1748</v>
+        <v>19710</v>
       </c>
       <c r="K3" t="n">
-        <v>1706</v>
+        <v>19450</v>
       </c>
       <c r="L3" t="n">
-        <v>1895</v>
+        <v>21850</v>
       </c>
       <c r="M3" t="n">
-        <v>1661</v>
+        <v>19450</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>3.32</v>
       </c>
       <c r="O3" t="n">
-        <v>43102357102</v>
+        <v>58294596590</v>
       </c>
       <c r="P3" t="n">
-        <v>2970</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>890</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X 직납 이슈로 인한 주가 급등 기대감. 최근 3일간 코스피 수익률 3위 기록.</t>
+          <t>로봇 테마와 연계된 보안주로 부각. 외국인 매수세 유입에도 불구하고 변동성 확대 및 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', '철강', '급등']</t>
+          <t>['보안', '로봇', '외국인']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>215250</v>
+        <v>1790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.26%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>459</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>2245</v>
+        <v>165</v>
       </c>
       <c r="H4" t="n">
-        <v>46.04</v>
+        <v>1.77</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>218000</v>
+        <v>1748</v>
       </c>
       <c r="K4" t="n">
-        <v>219500</v>
+        <v>1706</v>
       </c>
       <c r="L4" t="n">
-        <v>219500</v>
+        <v>1895</v>
       </c>
       <c r="M4" t="n">
-        <v>213000</v>
+        <v>1661</v>
       </c>
       <c r="N4" t="n">
-        <v>45.99</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>484740285250</v>
+        <v>46714111151</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>2970</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>890</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 관련 언급이 다수이며, 반도체 섹터 전반의 혼조세 속 삼성전자 주가 하락.</t>
+          <t>스페이스X 관련주로 부각되며 3일간 33.95%의 높은 수익률 기록. 2연상 기대감 및 물량 소화 움직임 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '하락']</t>
+          <t>['스페이스X', '철강', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42000</v>
+        <v>217000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>457</v>
       </c>
       <c r="G5" t="n">
-        <v>414</v>
+        <v>1651</v>
       </c>
       <c r="H5" t="n">
-        <v>13.11</v>
+        <v>46.04</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42950</v>
+        <v>218000</v>
       </c>
       <c r="K5" t="n">
-        <v>42600</v>
+        <v>219500</v>
       </c>
       <c r="L5" t="n">
-        <v>43200</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>41950</v>
+        <v>213000</v>
       </c>
       <c r="N5" t="n">
-        <v>13.04</v>
+        <v>45.99</v>
       </c>
       <c r="O5" t="n">
-        <v>3941269325</v>
+        <v>566813594250</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>C1 관련 FDA 승인 결과에 대한 기대와 우려 공존. 주가 방향성 불확실성.</t>
+          <t>반도체 업황 둔화 우려 및 공매도 이슈 지속. 샌디스크 급등에도 불구하고 약보합세로 마감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['C1', 'FDA 승인', '불확실성']</t>
+          <t>['반도체', '공매도', 'ETF']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1226000</v>
+        <v>42300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>535</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>1415</v>
+        <v>423</v>
       </c>
       <c r="H6" t="n">
-        <v>48.81</v>
+        <v>13.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1277000</v>
+        <v>42950</v>
       </c>
       <c r="K6" t="n">
-        <v>1265000</v>
+        <v>42600</v>
       </c>
       <c r="L6" t="n">
-        <v>1267000</v>
+        <v>43200</v>
       </c>
       <c r="M6" t="n">
-        <v>1213000</v>
+        <v>41900</v>
       </c>
       <c r="N6" t="n">
-        <v>48.82</v>
+        <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>764801157500</v>
+        <v>4591210800</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>465500</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구 및 경영진에 대한 강한 불만 표출. 주가 하락에 대한 부정적 전망.</t>
+          <t>C1 관련 FDA 승인 결과에 대한 기대와 우려 공존. 주가 방향성 불확실성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['솔리다임', '경영진', '하락']</t>
+          <t>['C1', 'FDA 승인', '불확실성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74400</v>
+        <v>1233000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-9.27%</t>
+          <t>'-3.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>547</v>
       </c>
       <c r="G7" t="n">
-        <v>140</v>
+        <v>1470</v>
       </c>
       <c r="H7" t="n">
-        <v>9.380000000000001</v>
+        <v>48.81</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,58 +1055,150 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>82000</v>
+        <v>1277000</v>
       </c>
       <c r="K7" t="n">
-        <v>79400</v>
+        <v>1265000</v>
       </c>
       <c r="L7" t="n">
-        <v>79400</v>
+        <v>1267000</v>
       </c>
       <c r="M7" t="n">
-        <v>73200</v>
+        <v>1213000</v>
       </c>
       <c r="N7" t="n">
-        <v>9.44</v>
+        <v>48.82</v>
       </c>
       <c r="O7" t="n">
-        <v>28816139450</v>
+        <v>869889540500</v>
       </c>
       <c r="P7" t="n">
-        <v>184000</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>44750</v>
+        <v>465500</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-168000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 비중 증가 및 주가 급락에 대한 불만. 투자자들의 부정적 심리 관찰.</t>
+          <t>솔리다임 상장 이슈로 인한 국장 전반의 약세에 영향. 최태원 회장 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '급락', '변동성']</t>
+          <t>['솔리다임', '상장', '반도체']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>75400</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-8.05%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="n">
+        <v>195</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L8" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M8" t="n">
+        <v>73200</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>33350528200</v>
+      </c>
+      <c r="P8" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-156000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>높은 공매도 비중과 함께 급락세. 적정가 논란 및 외국인 매도세에 대한 불만 제기.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['공매도', '급락', '기관']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>272210</t>
         </is>

--- a/data/trending_integrated_20261020_09.xlsx
+++ b/data/trending_integrated_20261020_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11150</v>
+        <v>11050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.26%</t>
+          <t>'+21.16%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -601,7 +601,7 @@
         <v>9500</v>
       </c>
       <c r="L2" t="n">
-        <v>11180</v>
+        <v>11250</v>
       </c>
       <c r="M2" t="n">
         <v>9470</v>
@@ -610,10 +610,10 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>111968802860</v>
+        <v>128700019745</v>
       </c>
       <c r="P2" t="n">
-        <v>11180</v>
+        <v>11250</v>
       </c>
       <c r="Q2" t="n">
         <v>2270</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 테마 복합으로 4일간 45.22% 급등. 7천억 수주잔고 기반 1조 시총 목표.</t>
+          <t>로봇, ESS, 2차전지 사업 관련 7천억 수주잔고. 1조 클럽 및 5~7만원 목표가 설정.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '수주잔고', '메가트렌드']</t>
+          <t>['로봇', '수주잔고', '목표가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20750</v>
+        <v>20850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.28%</t>
+          <t>'+5.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
         <v>3.07</v>
@@ -702,7 +702,7 @@
         <v>3.32</v>
       </c>
       <c r="O3" t="n">
-        <v>58294596590</v>
+        <v>63446211590</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 테마와 연계된 보안주로 부각. 외국인 매수세 유입에도 불구하고 변동성 확대 및 하락 가능성 언급.</t>
+          <t>로봇주 부각 속 보안 관련주로 언급. 대주주 매수 추정 및 1만 원 돌파 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안', '로봇', '외국인']</t>
+          <t>['보안주', '로봇', '대주주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1790</v>
+        <v>1775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+1.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="H4" t="n">
         <v>1.77</v>
@@ -794,7 +794,7 @@
         <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>46714111151</v>
+        <v>50615106263</v>
       </c>
       <c r="P4" t="n">
         <v>2970</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 부각되며 3일간 33.95%의 높은 수익률 기록. 2연상 기대감 및 물량 소화 움직임 관찰.</t>
+          <t>스페이스X 직납 관련 엄청난 호재 공시, 2연상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스페이스X', '철강', '테마']</t>
+          <t>['스페이스X', '호재', '수익률']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>217000</v>
+        <v>214250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G5" t="n">
-        <v>1651</v>
+        <v>1505</v>
       </c>
       <c r="H5" t="n">
         <v>46.04</v>
@@ -886,7 +886,7 @@
         <v>45.99</v>
       </c>
       <c r="O5" t="n">
-        <v>566813594250</v>
+        <v>664091008500</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 업황 둔화 우려 및 공매도 이슈 지속. 샌디스크 급등에도 불구하고 약보합세로 마감.</t>
+          <t>반도체 시장 종료 및 개미 털기 심리. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '공매도', 'ETF']</t>
+          <t>['반도체', '개미', '정치']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42300</v>
+        <v>42000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>4591210800</v>
+        <v>5346672825</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 관련 FDA 승인 결과에 대한 기대와 우려 공존. 주가 방향성 불확실성.</t>
+          <t>담관암 FDA 승인 기대감과 주가 미반영에 대한 의문. Class 1 발표 및 신뢰 회복 촉구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', 'FDA 승인', '불확실성']</t>
+          <t>['FDA승인', 'Class1', '신뢰']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1233000</v>
+        <v>1217000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.45%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="G7" t="n">
-        <v>1470</v>
+        <v>1546</v>
       </c>
       <c r="H7" t="n">
         <v>48.81</v>
@@ -1070,7 +1070,7 @@
         <v>48.82</v>
       </c>
       <c r="O7" t="n">
-        <v>869889540500</v>
+        <v>977871521500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈로 인한 국장 전반의 약세에 영향. 최태원 회장 관련 부정적 언급 다수.</t>
+          <t>솔리다임 상장 이슈로 인한 주가 폭락 우려. 경영진 신뢰도 하락.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '반도체']</t>
+          <t>['솔리다임', '주가폭락', '경영진']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75400</v>
+        <v>74500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-8.05%</t>
+          <t>'-9.15%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H8" t="n">
         <v>9.380000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.44</v>
       </c>
       <c r="O8" t="n">
-        <v>33350528200</v>
+        <v>37189469050</v>
       </c>
       <c r="P8" t="n">
         <v>184000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>높은 공매도 비중과 함께 급락세. 적정가 논란 및 외국인 매도세에 대한 불만 제기.</t>
+          <t>공매도 비중 증가 및 급락에 대한 불만. 시장 상황 및 외인/기관 움직임에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '급락', '기관']</t>
+          <t>['공매도', '급락', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">

--- a/data/trending_integrated_20261020_09.xlsx
+++ b/data/trending_integrated_20261020_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11050</v>
+        <v>11030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.16%</t>
+          <t>'+20.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.86</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>0.88</v>
@@ -610,7 +610,7 @@
         <v>1.74</v>
       </c>
       <c r="O2" t="n">
-        <v>128700019745</v>
+        <v>136632262835</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇, ESS, 2차전지 사업 관련 7천억 수주잔고. 1조 클럽 및 5~7만원 목표가 설정.</t>
+          <t>로봇 및 ESS 사업 성장 기대감에 따른 급등세 전망. 대규모 수주 잔고 확보 및 1조 클럽 진입 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '수주잔고', '목표가']</t>
+          <t>['로봇', '수주', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20850</v>
+        <v>20450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.78%</t>
+          <t>'+3.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H3" t="n">
         <v>3.07</v>
@@ -702,7 +702,7 @@
         <v>3.32</v>
       </c>
       <c r="O3" t="n">
-        <v>63446211590</v>
+        <v>67879285565</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇주 부각 속 보안 관련주로 언급. 대주주 매수 추정 및 1만 원 돌파 기대.</t>
+          <t>로봇 테마와 연계된 보안 사업 성장 가능성 언급. 외국인 매수세 유입 및 단기 변동성 확대 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '대주주']</t>
+          <t>['보안', '로봇', '외국인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1775</v>
+        <v>41950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>192</v>
+        <v>447</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77</v>
+        <v>13.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1748</v>
+        <v>42950</v>
       </c>
       <c r="K4" t="n">
-        <v>1706</v>
+        <v>42600</v>
       </c>
       <c r="L4" t="n">
-        <v>1895</v>
+        <v>43200</v>
       </c>
       <c r="M4" t="n">
-        <v>1661</v>
+        <v>41750</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>13.04</v>
       </c>
       <c r="O4" t="n">
-        <v>50615106263</v>
+        <v>5994598725</v>
       </c>
       <c r="P4" t="n">
-        <v>2970</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>890</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>260000</v>
+        <v>-5000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 직납 관련 엄청난 호재 공시, 2연상 기대감. 최근 3일간 코스피 수익률 3위 달성.</t>
+          <t>담관암 FDA 승인 기대감과 주가 미반영에 대한 의문. Class 1 발표 및 신뢰 회복 촉구.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '수익률']</t>
+          <t>['FDA승인', 'Class1', '신뢰']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214250</v>
+        <v>212500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-2.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="G5" t="n">
-        <v>1505</v>
+        <v>1405</v>
       </c>
       <c r="H5" t="n">
         <v>46.04</v>
@@ -880,13 +880,13 @@
         <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>213000</v>
+        <v>211500</v>
       </c>
       <c r="N5" t="n">
         <v>45.99</v>
       </c>
       <c r="O5" t="n">
-        <v>664091008500</v>
+        <v>772693100000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 시장 종료 및 개미 털기 심리. 정치적 이슈 언급.</t>
+          <t>반도체 시장 침체 및 증시 전반 하락세에 따른 부정적 전망. 정치적 이슈와 연계된 비관론 확산.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '개미', '정치']</t>
+          <t>['반도체', '침체', '하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42000</v>
+        <v>1690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>438</v>
+        <v>201</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>1.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>1748</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>1706</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>1895</v>
       </c>
       <c r="M6" t="n">
-        <v>41900</v>
+        <v>1661</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>5346672825</v>
+        <v>54929395449</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>2970</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>890</v>
       </c>
       <c r="R6" t="n">
-        <v>-5000</v>
+        <v>260000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감과 주가 미반영에 대한 의문. Class 1 발표 및 신뢰 회복 촉구.</t>
+          <t>스페이스X 관련 호재 공시 및 기대감으로 인한 급등세 전망. 외인 매수세 유입 및 코스피 수익률 상위 기록.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA승인', 'Class1', '신뢰']</t>
+          <t>['스페이스X', '호재', '급등']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1217000</v>
+        <v>14350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>571</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>1546</v>
+        <v>106</v>
       </c>
       <c r="H7" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1277000</v>
+        <v>14950</v>
       </c>
       <c r="K7" t="n">
-        <v>1265000</v>
+        <v>14610</v>
       </c>
       <c r="L7" t="n">
-        <v>1267000</v>
+        <v>14940</v>
       </c>
       <c r="M7" t="n">
-        <v>1213000</v>
+        <v>14290</v>
       </c>
       <c r="N7" t="n">
-        <v>48.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>977871521500</v>
+        <v>8933514345</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>465500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-168000</v>
+        <v>-23000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈로 인한 주가 폭락 우려. 경영진 신뢰도 하락.</t>
+          <t>실적 호조에도 불구하고 정치적 이슈 및 공매도 관련 부정적 논쟁 확산. 주가 부양 및 투명성 강화 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가폭락', '경영진']</t>
+          <t>['실적', '공매도', '정치']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74500</v>
+        <v>1203000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-9.15%</t>
+          <t>'-5.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>578</v>
       </c>
       <c r="G8" t="n">
-        <v>208</v>
+        <v>1498</v>
       </c>
       <c r="H8" t="n">
-        <v>9.380000000000001</v>
+        <v>48.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>82000</v>
+        <v>1277000</v>
       </c>
       <c r="K8" t="n">
-        <v>79400</v>
+        <v>1265000</v>
       </c>
       <c r="L8" t="n">
-        <v>79400</v>
+        <v>1267000</v>
       </c>
       <c r="M8" t="n">
-        <v>73200</v>
+        <v>1201000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.44</v>
+        <v>48.82</v>
       </c>
       <c r="O8" t="n">
-        <v>37189469050</v>
+        <v>1126268506500</v>
       </c>
       <c r="P8" t="n">
-        <v>184000</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>44750</v>
+        <v>465500</v>
       </c>
       <c r="R8" t="n">
-        <v>-156000</v>
+        <v>-168000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도 비중 증가 및 급락에 대한 불만. 시장 상황 및 외인/기관 움직임에 대한 부정적 인식.</t>
+          <t>솔리다임 상장 이슈와 경영진 불신으로 인한 주가 급락 및 부정적 전망. 반도체 산업 전반의 위기감 고조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,18 +1187,202 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '급락', '외인']</t>
+          <t>['솔리다임', '급락', '불신']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9060</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-6.79%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>41</v>
+      </c>
+      <c r="F9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>9720</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9930</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9930</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9010</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8015615490</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14940</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5390</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-235000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>테슬라 관련 기대감 및 거래량 증가세 확인. 공매도 세력의 압박 속에서도 상승 추세 유지 기대.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['테슬라', '거래량', '상승']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>74500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-9.15%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>74</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G10" t="n">
+        <v>226</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L10" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M10" t="n">
+        <v>73200</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O10" t="n">
+        <v>40403993300</v>
+      </c>
+      <c r="P10" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-156000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>공매도 비중 증가와 함께 주가 변동성 확대. 기관 및 외인 매매 동향에 따른 주가 흐름 예측.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['공매도', '변동성', '기관']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>272210</t>
         </is>
